--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOCAGE JOVENS L’ELIANA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>78.7336</v>
+        <v>75.02210000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>63.0226</v>
+        <v>56.7778</v>
       </c>
       <c r="F2" t="n">
-        <v>15.7107</v>
+        <v>18.2444</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6576</v>
+        <v>48.6617</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3285</v>
+        <v>32.538</v>
       </c>
       <c r="I2" t="n">
-        <v>8.328299999999999</v>
+        <v>16.1236</v>
       </c>
       <c r="J2" t="n">
-        <v>33.0199</v>
+        <v>73.2672</v>
       </c>
       <c r="K2" t="n">
-        <v>22.2492</v>
+        <v>52.2639</v>
       </c>
       <c r="L2" t="n">
-        <v>10.7707</v>
+        <v>21.0031</v>
       </c>
       <c r="M2" t="n">
-        <v>-19.3627</v>
+        <v>-24.6053</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.9205</v>
+        <v>-19.7259</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.4425</v>
+        <v>-4.8794</v>
       </c>
       <c r="P2" t="n">
-        <v>4.0316</v>
+        <v>7.3304</v>
       </c>
       <c r="Q2" t="n">
-        <v>-41.2331</v>
+        <v>-46.5476</v>
       </c>
       <c r="R2" t="n">
-        <v>45.2645</v>
+        <v>53.8777</v>
       </c>
       <c r="S2" t="n">
-        <v>39.0361</v>
+        <v>6.6075</v>
       </c>
       <c r="T2" t="n">
-        <v>31.8134</v>
+        <v>2.1226</v>
       </c>
       <c r="U2" t="n">
-        <v>7.2227</v>
+        <v>4.4855</v>
       </c>
       <c r="V2" t="n">
-        <v>22.0082</v>
+        <v>12.4222</v>
       </c>
       <c r="W2" t="n">
-        <v>39.4218</v>
+        <v>27.9359</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.4137</v>
+        <v>-15.5133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>64.5719</v>
+        <v>58.7661</v>
       </c>
       <c r="E3" t="n">
-        <v>38.6768</v>
+        <v>46.1699</v>
       </c>
       <c r="F3" t="n">
-        <v>25.895</v>
+        <v>12.5963</v>
       </c>
       <c r="G3" t="n">
-        <v>21.7705</v>
+        <v>13.6576</v>
       </c>
       <c r="H3" t="n">
-        <v>9.657</v>
+        <v>5.3285</v>
       </c>
       <c r="I3" t="n">
-        <v>12.1135</v>
+        <v>8.328299999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>47.9194</v>
+        <v>33.0199</v>
       </c>
       <c r="K3" t="n">
-        <v>32.6895</v>
+        <v>22.2492</v>
       </c>
       <c r="L3" t="n">
-        <v>15.2301</v>
+        <v>10.7707</v>
       </c>
       <c r="M3" t="n">
-        <v>-26.1489</v>
+        <v>-19.3627</v>
       </c>
       <c r="N3" t="n">
-        <v>-23.0323</v>
+        <v>-16.9205</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.1166</v>
+        <v>-2.4425</v>
       </c>
       <c r="P3" t="n">
-        <v>14.2941</v>
+        <v>4.0316</v>
       </c>
       <c r="Q3" t="n">
-        <v>-40.8665</v>
+        <v>-41.2331</v>
       </c>
       <c r="R3" t="n">
-        <v>55.1603</v>
+        <v>45.2645</v>
       </c>
       <c r="S3" t="n">
-        <v>34.013</v>
+        <v>19.0691</v>
       </c>
       <c r="T3" t="n">
-        <v>19.494</v>
+        <v>14.9608</v>
       </c>
       <c r="U3" t="n">
-        <v>14.5194</v>
+        <v>4.1083</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.5061</v>
+        <v>22.0082</v>
       </c>
       <c r="W3" t="n">
-        <v>12.13</v>
+        <v>39.4218</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.6361</v>
+        <v>-17.4137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>58.0458</v>
+        <v>50.7139</v>
       </c>
       <c r="E4" t="n">
-        <v>45.965</v>
+        <v>29.4075</v>
       </c>
       <c r="F4" t="n">
-        <v>12.0807</v>
+        <v>21.307</v>
       </c>
       <c r="G4" t="n">
-        <v>48.6617</v>
+        <v>21.7705</v>
       </c>
       <c r="H4" t="n">
-        <v>32.538</v>
+        <v>9.657</v>
       </c>
       <c r="I4" t="n">
-        <v>16.1236</v>
+        <v>12.1135</v>
       </c>
       <c r="J4" t="n">
-        <v>73.2672</v>
+        <v>47.9194</v>
       </c>
       <c r="K4" t="n">
-        <v>52.2639</v>
+        <v>32.6895</v>
       </c>
       <c r="L4" t="n">
-        <v>21.0031</v>
+        <v>15.2301</v>
       </c>
       <c r="M4" t="n">
-        <v>-24.6053</v>
+        <v>-26.1489</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.7259</v>
+        <v>-23.0323</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.8794</v>
+        <v>-3.1166</v>
       </c>
       <c r="P4" t="n">
-        <v>7.3304</v>
+        <v>14.2941</v>
       </c>
       <c r="Q4" t="n">
-        <v>-46.5476</v>
+        <v>-40.8665</v>
       </c>
       <c r="R4" t="n">
-        <v>53.8777</v>
+        <v>55.1603</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.3684</v>
+        <v>20.1556</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.6904</v>
+        <v>10.2242</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.6782</v>
+        <v>9.9312</v>
       </c>
       <c r="V4" t="n">
-        <v>12.4222</v>
+        <v>-5.5061</v>
       </c>
       <c r="W4" t="n">
-        <v>27.9359</v>
+        <v>12.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.5133</v>
+        <v>-17.6361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>35.1082</v>
+        <v>28.6073</v>
       </c>
       <c r="E5" t="n">
-        <v>29.2369</v>
+        <v>28.6073</v>
       </c>
       <c r="F5" t="n">
-        <v>5.871300000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>16.7462</v>
+        <v>28.6073</v>
       </c>
       <c r="H5" t="n">
-        <v>12.3874</v>
+        <v>12.3541</v>
       </c>
       <c r="I5" t="n">
-        <v>4.359000000000001</v>
+        <v>16.2526</v>
       </c>
       <c r="J5" t="n">
-        <v>34.649</v>
+        <v>28.6073</v>
       </c>
       <c r="K5" t="n">
-        <v>25.83</v>
+        <v>12.3541</v>
       </c>
       <c r="L5" t="n">
-        <v>8.8187</v>
+        <v>16.2526</v>
       </c>
       <c r="M5" t="n">
-        <v>-17.903</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-13.4427</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.46</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.382</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-30.604</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>32.9862</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>15.5146</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>12.4076</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.107</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4650999999999998</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>12.7842</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.3191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>28.6073</v>
+        <v>28.0435</v>
       </c>
       <c r="E6" t="n">
-        <v>28.6073</v>
+        <v>22.26</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.7834</v>
       </c>
       <c r="G6" t="n">
-        <v>28.6073</v>
+        <v>16.7462</v>
       </c>
       <c r="H6" t="n">
-        <v>12.3541</v>
+        <v>12.3874</v>
       </c>
       <c r="I6" t="n">
-        <v>16.2526</v>
+        <v>4.359000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>28.6073</v>
+        <v>34.649</v>
       </c>
       <c r="K6" t="n">
-        <v>12.3541</v>
+        <v>25.83</v>
       </c>
       <c r="L6" t="n">
-        <v>16.2526</v>
+        <v>8.8187</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-17.903</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-13.4427</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-4.46</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-30.604</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>32.9862</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>8.4503</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>5.4312</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.0193</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4650999999999998</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>12.7842</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-12.3191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>13.3782</v>
+        <v>14.4505</v>
       </c>
       <c r="E7" t="n">
-        <v>13.3782</v>
+        <v>5.327</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>9.1236</v>
       </c>
       <c r="G7" t="n">
-        <v>13.3782</v>
+        <v>11.4949</v>
       </c>
       <c r="H7" t="n">
-        <v>6.502</v>
+        <v>-1.124399999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8761</v>
+        <v>12.6189</v>
       </c>
       <c r="J7" t="n">
-        <v>13.3782</v>
+        <v>24.7936</v>
       </c>
       <c r="K7" t="n">
-        <v>6.502</v>
+        <v>11.4974</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8761</v>
+        <v>13.2962</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-13.2991</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-12.6216</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.6773</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.0474</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-29.3213</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>35.3687</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9257</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8236</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1022999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-6.017199999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>7.0308</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-13.0479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>9.588999999999999</v>
+        <v>13.3782</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7018000000000004</v>
+        <v>13.3782</v>
       </c>
       <c r="F8" t="n">
-        <v>10.291</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.459199999999999</v>
+        <v>13.3782</v>
       </c>
       <c r="H8" t="n">
-        <v>12.6174</v>
+        <v>6.502</v>
       </c>
       <c r="I8" t="n">
-        <v>-17.0769</v>
+        <v>6.8761</v>
       </c>
       <c r="J8" t="n">
-        <v>28.7661</v>
+        <v>13.3782</v>
       </c>
       <c r="K8" t="n">
-        <v>37.8208</v>
+        <v>6.502</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.0548</v>
+        <v>6.8761</v>
       </c>
       <c r="M8" t="n">
-        <v>-33.2251</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-25.2034</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.021799999999999</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2987</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-59.7418</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>63.0404</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>14.4258</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>6.284000000000001</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>8.141999999999999</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.6759</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>23.9896</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-27.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. CAPOUE</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>6.6718</v>
+        <v>10.921</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5514</v>
+        <v>1.3477</v>
       </c>
       <c r="F9" t="n">
-        <v>4.120200000000001</v>
+        <v>9.5731</v>
       </c>
       <c r="G9" t="n">
-        <v>8.061300000000001</v>
+        <v>-4.459199999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4578</v>
+        <v>12.6174</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3966</v>
+        <v>-17.0769</v>
       </c>
       <c r="J9" t="n">
-        <v>10.9685</v>
+        <v>28.7661</v>
       </c>
       <c r="K9" t="n">
-        <v>14.3569</v>
+        <v>37.8208</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3886</v>
+        <v>-9.0548</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9072</v>
+        <v>-33.2251</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.8992</v>
+        <v>-25.2034</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9921000000000001</v>
+        <v>-8.021799999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>4.0316</v>
+        <v>3.2987</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.529399999999999</v>
+        <v>-59.7418</v>
       </c>
       <c r="R9" t="n">
-        <v>13.5611</v>
+        <v>63.0404</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2642</v>
+        <v>15.7572</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4269999999999999</v>
+        <v>8.3337</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.6912</v>
+        <v>7.4237</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.157</v>
+        <v>-3.6759</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6855000000000001</v>
+        <v>23.9896</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8427</v>
+        <v>-27.6659</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>4.501200000000001</v>
+        <v>10.0618</v>
       </c>
       <c r="E10" t="n">
-        <v>6.8288</v>
+        <v>3.508899999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3276</v>
+        <v>6.553199999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6649</v>
+        <v>-2.2218</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7822</v>
+        <v>-3.5713</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1173999999999995</v>
+        <v>1.349399999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>20.9889</v>
+        <v>18.4302</v>
       </c>
       <c r="K10" t="n">
-        <v>17.7685</v>
+        <v>11.7547</v>
       </c>
       <c r="L10" t="n">
-        <v>3.220199999999999</v>
+        <v>6.675199999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.324</v>
+        <v>-20.6518</v>
       </c>
       <c r="N10" t="n">
-        <v>-11.9866</v>
+        <v>-15.3262</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.3376</v>
+        <v>-5.3259</v>
       </c>
       <c r="P10" t="n">
-        <v>-13.5611</v>
+        <v>9.5291</v>
       </c>
       <c r="Q10" t="n">
-        <v>-40.1333</v>
+        <v>-23.8236</v>
       </c>
       <c r="R10" t="n">
-        <v>26.5724</v>
+        <v>33.3526</v>
       </c>
       <c r="S10" t="n">
-        <v>17.0479</v>
+        <v>1.8507</v>
       </c>
       <c r="T10" t="n">
-        <v>13.5628</v>
+        <v>1.8609</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4847</v>
+        <v>-0.01020000000000024</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.6504</v>
+        <v>0.9035000000000003</v>
       </c>
       <c r="W10" t="n">
-        <v>12.4104</v>
+        <v>7.041099999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.0606</v>
+        <v>-6.1377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AVIÑO GOMEZ-SENENT</t>
+          <t>E. CAPOUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8762</v>
+        <v>10.034</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8762</v>
+        <v>3.8156</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>6.2186</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8762</v>
+        <v>8.061300000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2511</v>
+        <v>10.4578</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6251</v>
+        <v>-2.3966</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8762</v>
+        <v>10.9685</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2511</v>
+        <v>14.3569</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6251</v>
+        <v>-3.3886</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-2.9072</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-3.8992</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.9921000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.0316</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-9.529399999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>13.5611</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.0982</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.6909</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.5929</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-3.157</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6855000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.8427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. PERIS GADEA</t>
+          <t>J. AVIÑO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6888000000000001</v>
+        <v>3.8762</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1309</v>
+        <v>3.8762</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5577000000000001</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9107</v>
+        <v>3.8762</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1701000000000001</v>
+        <v>3.2511</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7405999999999999</v>
+        <v>0.6251</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6662</v>
+        <v>3.8762</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9319000000000001</v>
+        <v>3.2511</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7343</v>
+        <v>0.6251</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5771</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1022</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4749</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0996</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0996</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4012</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6977</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2965</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. TABOADA REDONDO</t>
+          <t>R. PERIS GADEA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.3289</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4472</v>
+        <v>0.2536999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6654</v>
+        <v>-0.5827</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8974</v>
+        <v>-0.9107</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.641</v>
+        <v>-0.1701000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2564</v>
+        <v>-0.7405999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2821</v>
+        <v>1.6662</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.641</v>
+        <v>0.9319000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.641</v>
+        <v>0.7343</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3846</v>
+        <v>-2.5771</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-1.1022</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3846</v>
+        <v>-1.4749</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1833</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.0996</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1833</v>
+        <v>1.0996</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1652</v>
+        <v>-0.313</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0975</v>
+        <v>0.2716</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>R. TABOADA REDONDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.199300000000001</v>
+        <v>-0.5677</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.5232</v>
+        <v>-1.1587</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3241</v>
+        <v>0.5911</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4949</v>
+        <v>-0.8974</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.124399999999999</v>
+        <v>-0.641</v>
       </c>
       <c r="I14" t="n">
-        <v>12.6189</v>
+        <v>-0.2564</v>
       </c>
       <c r="J14" t="n">
-        <v>24.7936</v>
+        <v>-1.2821</v>
       </c>
       <c r="K14" t="n">
-        <v>11.4974</v>
+        <v>-0.641</v>
       </c>
       <c r="L14" t="n">
-        <v>13.2962</v>
+        <v>-0.641</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.2991</v>
+        <v>0.3846</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.6216</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6773</v>
+        <v>0.3846</v>
       </c>
       <c r="P14" t="n">
-        <v>6.0474</v>
+        <v>0.1833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-29.3213</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>35.3687</v>
+        <v>0.1833</v>
       </c>
       <c r="S14" t="n">
-        <v>-12.724</v>
+        <v>0.1465</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.0268</v>
+        <v>0.1233</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.6972</v>
+        <v>0.0232</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.017199999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>7.0308</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.0479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MAINER SAEZ</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8689</v>
+        <v>-0.8911000000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7353999999999998</v>
+        <v>-1.3961</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1336</v>
+        <v>0.5050999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2191000000000001</v>
+        <v>-6.121799999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.28</v>
+        <v>-2.3634</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06079999999999997</v>
+        <v>-3.7583</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6846</v>
+        <v>7.5534</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9504</v>
+        <v>7.525700000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7341999999999999</v>
+        <v>0.02820000000000038</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9037</v>
+        <v>-13.6753</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2302</v>
+        <v>-9.889099999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6735</v>
+        <v>-3.7865</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1832</v>
+        <v>8.7965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8326</v>
+        <v>-15.7601</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6494</v>
+        <v>24.5563</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1341</v>
+        <v>0.09219999999999989</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5876</v>
+        <v>1.1093</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5468</v>
+        <v>-1.0172</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3324</v>
+        <v>-3.6575</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.701499999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3324</v>
+        <v>-9.3589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. TABOADA REDONDO</t>
+          <t>L. MAINER SAEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.2418</v>
+        <v>-1.0963</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0032</v>
+        <v>-0.1857000000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2385</v>
+        <v>-0.9106</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9358</v>
+        <v>-0.2191000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9518</v>
+        <v>-0.28</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.984</v>
+        <v>0.06079999999999997</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8381</v>
+        <v>1.6846</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5977</v>
+        <v>0.9504</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2404</v>
+        <v>0.7341999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0977</v>
+        <v>-1.9037</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3541</v>
+        <v>-1.2302</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2564</v>
+        <v>-0.6735</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.1832</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.6494</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.306</v>
+        <v>-0.3615</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1652</v>
+        <v>-0.03780000000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1408</v>
+        <v>-0.3237</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>Y. TABOADA REDONDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7962</v>
+        <v>-1.4775</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.9542</v>
+        <v>-1.4123</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1583</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2218</v>
+        <v>-1.9358</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.5713</v>
+        <v>-0.9518</v>
       </c>
       <c r="I17" t="n">
-        <v>1.349399999999999</v>
+        <v>-0.984</v>
       </c>
       <c r="J17" t="n">
-        <v>18.4302</v>
+        <v>-1.8381</v>
       </c>
       <c r="K17" t="n">
-        <v>11.7547</v>
+        <v>-0.5977</v>
       </c>
       <c r="L17" t="n">
-        <v>6.675199999999999</v>
+        <v>-1.2404</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.6518</v>
+        <v>-0.0977</v>
       </c>
       <c r="N17" t="n">
-        <v>-15.3262</v>
+        <v>-0.3541</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.3259</v>
+        <v>0.2564</v>
       </c>
       <c r="P17" t="n">
-        <v>9.5291</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23.8236</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>33.3526</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.0072</v>
+        <v>0.4583</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.6022</v>
+        <v>0.4257</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.4048</v>
+        <v>0.0326</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9035000000000003</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>7.041099999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.1377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. TATO SAPENA</t>
+          <t>A. MORAL SANMARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.537199999999999</v>
+        <v>-2.7576</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8178</v>
+        <v>-1.7014</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7194</v>
+        <v>-1.0564</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.863599999999999</v>
+        <v>-3.629199999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.0235</v>
+        <v>-1.963199999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.16</v>
+        <v>-1.6661</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.369</v>
+        <v>5.6775</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.369</v>
+        <v>7.1165</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.438899999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4945</v>
+        <v>-9.306699999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6546</v>
+        <v>-9.079699999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.16</v>
+        <v>-0.2271000000000002</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>0.7331</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-16.8597</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0996</v>
+        <v>17.5928</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5898</v>
+        <v>1.0728</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5325</v>
+        <v>-0.09440000000000004</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.05750000000000001</v>
+        <v>1.1675</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.267</v>
+        <v>-0.9346000000000005</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>9.575099999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>-10.5097</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORAL SANMARTIN</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.7818</v>
+        <v>-2.858000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.1883</v>
+        <v>-0.3130000000000006</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5936</v>
+        <v>-2.545</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.629199999999999</v>
+        <v>5.6649</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.963199999999999</v>
+        <v>5.7822</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6661</v>
+        <v>-0.1173999999999995</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6775</v>
+        <v>20.9889</v>
       </c>
       <c r="K19" t="n">
-        <v>7.1165</v>
+        <v>17.7685</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.438899999999999</v>
+        <v>3.220199999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.306699999999999</v>
+        <v>-15.324</v>
       </c>
       <c r="N19" t="n">
-        <v>-9.079699999999999</v>
+        <v>-11.9866</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2271000000000002</v>
+        <v>-3.3376</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7331</v>
+        <v>-13.5611</v>
       </c>
       <c r="Q19" t="n">
-        <v>-16.8597</v>
+        <v>-40.1333</v>
       </c>
       <c r="R19" t="n">
-        <v>17.5928</v>
+        <v>26.5724</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.9511</v>
+        <v>9.688700000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.5813</v>
+        <v>6.4211</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3699</v>
+        <v>3.2679</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9346000000000005</v>
+        <v>-4.6504</v>
       </c>
       <c r="W19" t="n">
-        <v>9.575099999999999</v>
+        <v>12.4104</v>
       </c>
       <c r="X19" t="n">
-        <v>-10.5097</v>
+        <v>-17.0606</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>C. TATO SAPENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>-14.8934</v>
+        <v>-4.5261</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.1363</v>
+        <v>-2.8563</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7574</v>
+        <v>-1.6699</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.121799999999999</v>
+        <v>-3.863599999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3634</v>
+        <v>-4.0235</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7583</v>
+        <v>0.16</v>
       </c>
       <c r="J20" t="n">
-        <v>7.5534</v>
+        <v>-2.369</v>
       </c>
       <c r="K20" t="n">
-        <v>7.525700000000001</v>
+        <v>-2.369</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02820000000000038</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-13.6753</v>
+        <v>-1.4945</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.889099999999999</v>
+        <v>-1.6546</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.7865</v>
+        <v>0.16</v>
       </c>
       <c r="P20" t="n">
-        <v>8.7965</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-15.7601</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>24.5563</v>
+        <v>1.0996</v>
       </c>
       <c r="S20" t="n">
-        <v>-13.9103</v>
+        <v>0.4211</v>
       </c>
       <c r="T20" t="n">
-        <v>-8.6312</v>
+        <v>0.4292</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.2794</v>
+        <v>-0.007799999999999974</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6575</v>
+        <v>-1.267</v>
       </c>
       <c r="W20" t="n">
-        <v>5.701499999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-9.3589</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>-28.3049</v>
+        <v>-25.8117</v>
       </c>
       <c r="E21" t="n">
-        <v>-33.0156</v>
+        <v>-31.312</v>
       </c>
       <c r="F21" t="n">
-        <v>4.710699999999999</v>
+        <v>5.5002</v>
       </c>
       <c r="G21" t="n">
         <v>-17.0619</v>
@@ -2092,13 +2092,13 @@
         <v>15.2104</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9159</v>
+        <v>0.5772</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.5247</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6087</v>
+        <v>1.3983</v>
       </c>
       <c r="V21" t="n">
         <v>-8.0443</v>
@@ -2125,13 +2125,13 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>237.9891</v>
+        <v>263.5597</v>
       </c>
       <c r="E22" t="n">
-        <v>165.4893</v>
+        <v>174.3943</v>
       </c>
       <c r="F22" t="n">
-        <v>72.4996</v>
+        <v>89.16630000000001</v>
       </c>
       <c r="G22" t="n">
         <v>130.5983</v>
@@ -2158,28 +2158,28 @@
         <v>-172.0871</v>
       </c>
       <c r="O22" t="n">
-        <v>-32.75319999999999</v>
+        <v>-32.7532</v>
       </c>
       <c r="P22" t="n">
-        <v>45.81420000000001</v>
+        <v>45.81419999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-374.7623</v>
       </c>
       <c r="R22" t="n">
-        <v>420.5753000000001</v>
+        <v>420.5753</v>
       </c>
       <c r="S22" t="n">
-        <v>62.3976</v>
+        <v>87.96829999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>45.78399999999999</v>
+        <v>54.6902</v>
       </c>
       <c r="U22" t="n">
-        <v>16.6127</v>
+        <v>33.2796</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8202999999999978</v>
+        <v>-0.820299999999996</v>
       </c>
       <c r="W22" t="n">
         <v>159.0279</v>
